--- a/research/traditional_assets/database/data/saint_lucia/saint_lucia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/saint_lucia/saint_lucia_financial_svcs_non_bank_insurance.xlsx
@@ -594,34 +594,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.7283018867924528</v>
+        <v>0.5467532467532468</v>
       </c>
       <c r="J2">
-        <v>0.7207677293428757</v>
+        <v>0.5296923960560325</v>
       </c>
       <c r="K2">
-        <v>5.74</v>
+        <v>3.94</v>
       </c>
       <c r="L2">
-        <v>0.5415094339622641</v>
+        <v>0.2558441558441558</v>
       </c>
       <c r="M2">
-        <v>1.69</v>
+        <v>2.98</v>
       </c>
       <c r="N2">
-        <v>0.02918825561312608</v>
+        <v>0.0495016611295681</v>
       </c>
       <c r="O2">
-        <v>0.2944250871080139</v>
+        <v>0.7563451776649747</v>
       </c>
       <c r="P2">
-        <v>1.69</v>
+        <v>2.98</v>
       </c>
       <c r="Q2">
-        <v>0.02918825561312608</v>
+        <v>0.0495016611295681</v>
       </c>
       <c r="R2">
-        <v>0.2944250871080139</v>
+        <v>0.7563451776649747</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,67 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.06</v>
+        <v>5.9</v>
       </c>
       <c r="V2">
-        <v>0.01830742659758204</v>
+        <v>0.09800664451827243</v>
       </c>
       <c r="W2">
-        <v>0.1526595744680851</v>
+        <v>0.05907046476761619</v>
       </c>
       <c r="X2">
-        <v>0.04280980799185248</v>
+        <v>0.08854351422922518</v>
       </c>
       <c r="Y2">
-        <v>0.1098497664762326</v>
+        <v>-0.029473049461609</v>
       </c>
       <c r="Z2">
-        <v>0.1752066115702479</v>
+        <v>0.1731504384978637</v>
       </c>
       <c r="AA2">
-        <v>0.1262832715873468</v>
+        <v>0.09171647064608612</v>
       </c>
       <c r="AB2">
-        <v>0.05009605249203644</v>
+        <v>0.09153397033065697</v>
       </c>
       <c r="AC2">
-        <v>0.07618721909531037</v>
+        <v>0.0001825003154291571</v>
       </c>
       <c r="AD2">
-        <v>23.3</v>
+        <v>68.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>23.3</v>
+        <v>68.2</v>
       </c>
       <c r="AG2">
-        <v>22.24</v>
+        <v>62.3</v>
       </c>
       <c r="AH2">
-        <v>0.2869458128078818</v>
+        <v>0.5311526479750779</v>
       </c>
       <c r="AI2">
-        <v>0.2588888888888889</v>
+        <v>0.5025792188651438</v>
       </c>
       <c r="AJ2">
-        <v>0.2775143498876966</v>
+        <v>0.5085714285714286</v>
       </c>
       <c r="AK2">
-        <v>0.250056217674837</v>
+        <v>0.4799691833590138</v>
       </c>
       <c r="AL2">
-        <v>1.8</v>
+        <v>3.92</v>
       </c>
       <c r="AM2">
-        <v>1.8</v>
+        <v>3.92</v>
       </c>
       <c r="AO2">
-        <v>4.288888888888889</v>
+        <v>2.147959183673469</v>
       </c>
       <c r="AQ2">
-        <v>4.288888888888889</v>
+        <v>2.147959183673469</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +716,34 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.7283018867924528</v>
+        <v>0.5467532467532468</v>
       </c>
       <c r="J3">
-        <v>0.7207677293428757</v>
+        <v>0.5296923960560325</v>
       </c>
       <c r="K3">
-        <v>5.74</v>
+        <v>3.94</v>
       </c>
       <c r="L3">
-        <v>0.5415094339622641</v>
+        <v>0.2558441558441558</v>
       </c>
       <c r="M3">
-        <v>1.69</v>
+        <v>2.98</v>
       </c>
       <c r="N3">
-        <v>0.02918825561312608</v>
+        <v>0.0495016611295681</v>
       </c>
       <c r="O3">
-        <v>0.2944250871080139</v>
+        <v>0.7563451776649747</v>
       </c>
       <c r="P3">
-        <v>1.69</v>
+        <v>2.98</v>
       </c>
       <c r="Q3">
-        <v>0.02918825561312608</v>
+        <v>0.0495016611295681</v>
       </c>
       <c r="R3">
-        <v>0.2944250871080139</v>
+        <v>0.7563451776649747</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,67 +752,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.06</v>
+        <v>5.9</v>
       </c>
       <c r="V3">
-        <v>0.01830742659758204</v>
+        <v>0.09800664451827243</v>
       </c>
       <c r="W3">
-        <v>0.1526595744680851</v>
+        <v>0.05907046476761619</v>
       </c>
       <c r="X3">
-        <v>0.04280980799185248</v>
+        <v>0.08854351422922518</v>
       </c>
       <c r="Y3">
-        <v>0.1098497664762326</v>
+        <v>-0.029473049461609</v>
       </c>
       <c r="Z3">
-        <v>0.1752066115702479</v>
+        <v>0.1731504384978637</v>
       </c>
       <c r="AA3">
-        <v>0.1262832715873468</v>
+        <v>0.09171647064608612</v>
       </c>
       <c r="AB3">
-        <v>0.05009605249203644</v>
+        <v>0.09153397033065697</v>
       </c>
       <c r="AC3">
-        <v>0.07618721909531037</v>
+        <v>0.0001825003154291571</v>
       </c>
       <c r="AD3">
-        <v>23.3</v>
+        <v>68.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>23.3</v>
+        <v>68.2</v>
       </c>
       <c r="AG3">
-        <v>22.24</v>
+        <v>62.3</v>
       </c>
       <c r="AH3">
-        <v>0.2869458128078818</v>
+        <v>0.5311526479750779</v>
       </c>
       <c r="AI3">
-        <v>0.2588888888888889</v>
+        <v>0.5025792188651438</v>
       </c>
       <c r="AJ3">
-        <v>0.2775143498876966</v>
+        <v>0.5085714285714286</v>
       </c>
       <c r="AK3">
-        <v>0.250056217674837</v>
+        <v>0.4799691833590138</v>
       </c>
       <c r="AL3">
-        <v>1.8</v>
+        <v>3.92</v>
       </c>
       <c r="AM3">
-        <v>1.8</v>
+        <v>3.92</v>
       </c>
       <c r="AO3">
-        <v>4.288888888888889</v>
+        <v>2.147959183673469</v>
       </c>
       <c r="AQ3">
-        <v>4.288888888888889</v>
+        <v>2.147959183673469</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/saint_lucia/saint_lucia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/saint_lucia/saint_lucia_financial_svcs_non_bank_insurance.xlsx
@@ -587,6 +587,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.467</v>
+      </c>
+      <c r="E2">
+        <v>0.329</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -594,103 +600,103 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.5467532467532468</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J2">
-        <v>0.5296923960560325</v>
+        <v>0.6667768882701011</v>
       </c>
       <c r="K2">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="L2">
-        <v>0.2558441558441558</v>
+        <v>0.2724358974358975</v>
       </c>
       <c r="M2">
-        <v>2.98</v>
+        <v>2.703</v>
       </c>
       <c r="N2">
-        <v>0.0495016611295681</v>
+        <v>0.06271461716937354</v>
       </c>
       <c r="O2">
-        <v>0.7563451776649747</v>
+        <v>0.636</v>
       </c>
       <c r="P2">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="Q2">
-        <v>0.0495016611295681</v>
+        <v>0.05707656612529002</v>
       </c>
       <c r="R2">
-        <v>0.7563451776649747</v>
+        <v>0.5788235294117647</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.2429999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0899001109877913</v>
       </c>
       <c r="U2">
-        <v>5.9</v>
+        <v>2.57</v>
       </c>
       <c r="V2">
-        <v>0.09800664451827243</v>
+        <v>0.05962877030162413</v>
       </c>
       <c r="W2">
-        <v>0.05907046476761619</v>
+        <v>0.06296296296296296</v>
       </c>
       <c r="X2">
-        <v>0.08854351422922518</v>
+        <v>0.177912764632137</v>
       </c>
       <c r="Y2">
-        <v>-0.029473049461609</v>
+        <v>-0.114949801669174</v>
       </c>
       <c r="Z2">
-        <v>0.1731504384978637</v>
+        <v>0.1201848998459168</v>
       </c>
       <c r="AA2">
-        <v>0.09171647064608612</v>
+        <v>0.08013651353631415</v>
       </c>
       <c r="AB2">
-        <v>0.09153397033065697</v>
+        <v>0.1361015564078789</v>
       </c>
       <c r="AC2">
-        <v>0.0001825003154291571</v>
+        <v>-0.05596504287156476</v>
       </c>
       <c r="AD2">
-        <v>68.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>68.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>62.3</v>
+        <v>85.53</v>
       </c>
       <c r="AH2">
-        <v>0.5311526479750779</v>
+        <v>0.6714939024390244</v>
       </c>
       <c r="AI2">
-        <v>0.5025792188651438</v>
+        <v>0.5607893061744111</v>
       </c>
       <c r="AJ2">
-        <v>0.5085714285714286</v>
+        <v>0.6649304205861775</v>
       </c>
       <c r="AK2">
-        <v>0.4799691833590138</v>
+        <v>0.55348476024073</v>
       </c>
       <c r="AL2">
-        <v>3.92</v>
+        <v>6.61</v>
       </c>
       <c r="AM2">
-        <v>3.92</v>
+        <v>6.61</v>
       </c>
       <c r="AO2">
-        <v>2.147959183673469</v>
+        <v>1.633888048411498</v>
       </c>
       <c r="AQ2">
-        <v>2.147959183673469</v>
+        <v>1.633888048411498</v>
       </c>
     </row>
     <row r="3">
@@ -709,6 +715,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.467</v>
+      </c>
+      <c r="E3">
+        <v>0.329</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -716,103 +728,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.5467532467532468</v>
+        <v>0.6923076923076924</v>
       </c>
       <c r="J3">
-        <v>0.5296923960560325</v>
+        <v>0.6667768882701011</v>
       </c>
       <c r="K3">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="L3">
-        <v>0.2558441558441558</v>
+        <v>0.2724358974358975</v>
       </c>
       <c r="M3">
-        <v>2.98</v>
+        <v>2.703</v>
       </c>
       <c r="N3">
-        <v>0.0495016611295681</v>
+        <v>0.06271461716937354</v>
       </c>
       <c r="O3">
-        <v>0.7563451776649747</v>
+        <v>0.636</v>
       </c>
       <c r="P3">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="Q3">
-        <v>0.0495016611295681</v>
+        <v>0.05707656612529002</v>
       </c>
       <c r="R3">
-        <v>0.7563451776649747</v>
+        <v>0.5788235294117647</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.2429999999999999</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>0.0899001109877913</v>
       </c>
       <c r="U3">
-        <v>5.9</v>
+        <v>2.57</v>
       </c>
       <c r="V3">
-        <v>0.09800664451827243</v>
+        <v>0.05962877030162413</v>
       </c>
       <c r="W3">
-        <v>0.05907046476761619</v>
+        <v>0.06296296296296296</v>
       </c>
       <c r="X3">
-        <v>0.08854351422922518</v>
+        <v>0.177912764632137</v>
       </c>
       <c r="Y3">
-        <v>-0.029473049461609</v>
+        <v>-0.114949801669174</v>
       </c>
       <c r="Z3">
-        <v>0.1731504384978637</v>
+        <v>0.1201848998459168</v>
       </c>
       <c r="AA3">
-        <v>0.09171647064608612</v>
+        <v>0.08013651353631415</v>
       </c>
       <c r="AB3">
-        <v>0.09153397033065697</v>
+        <v>0.1361015564078789</v>
       </c>
       <c r="AC3">
-        <v>0.0001825003154291571</v>
+        <v>-0.05596504287156476</v>
       </c>
       <c r="AD3">
-        <v>68.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>68.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="AG3">
-        <v>62.3</v>
+        <v>85.53</v>
       </c>
       <c r="AH3">
-        <v>0.5311526479750779</v>
+        <v>0.6714939024390244</v>
       </c>
       <c r="AI3">
-        <v>0.5025792188651438</v>
+        <v>0.5607893061744111</v>
       </c>
       <c r="AJ3">
-        <v>0.5085714285714286</v>
+        <v>0.6649304205861775</v>
       </c>
       <c r="AK3">
-        <v>0.4799691833590138</v>
+        <v>0.55348476024073</v>
       </c>
       <c r="AL3">
-        <v>3.92</v>
+        <v>6.61</v>
       </c>
       <c r="AM3">
-        <v>3.92</v>
+        <v>6.61</v>
       </c>
       <c r="AO3">
-        <v>2.147959183673469</v>
+        <v>1.633888048411498</v>
       </c>
       <c r="AQ3">
-        <v>2.147959183673469</v>
+        <v>1.633888048411498</v>
       </c>
     </row>
   </sheetData>
